--- a/features/testdata/contractor_employee-fails.xlsx
+++ b/features/testdata/contractor_employee-fails.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CLMS-Automation\testing-framework-playwright--simplecode\features\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B75F69D-894C-4F3D-8C89-66B091A7987B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFAD67E3-C3B6-4650-A43E-804E9CE325F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ContratorEmployee" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="185">
   <si>
     <t>EmployeeCode</t>
   </si>
@@ -577,6 +577,9 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -1816,7 +1819,16 @@
         <v>174</v>
       </c>
       <c r="BQ2" s="3">
-        <v>965236585254</v>
+        <v>965200005050</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>184</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>184</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>184</v>
       </c>
       <c r="CY2" t="s">
         <v>160</v>
@@ -1972,7 +1984,7 @@
         <v>1004</v>
       </c>
       <c r="BQ3" s="3">
-        <v>965211180204</v>
+        <v>965000080200</v>
       </c>
     </row>
     <row r="4" spans="1:152" x14ac:dyDescent="0.25">
